--- a/assets/docs/支撑材料索引.xlsx
+++ b/assets/docs/支撑材料索引.xlsx
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2023年体质测试识别并纳入管理</t>
+          <t>学校报告为纳入管理数；媒体按BMI&gt;28报道341人，二者关系待核</t>
         </is>
       </c>
     </row>
